--- a/src/main/resources/static/expert-form/expert-form.xlsx
+++ b/src/main/resources/static/expert-form/expert-form.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10910"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0AA71A-8D19-684E-A72A-0B039C918294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
-    <sheet name="Лист2" sheetId="2" r:id="rId2"/>
+    <sheet name="Рецензия" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="51">
   <si>
     <t>СОДЕРЖАНИЕ</t>
   </si>
@@ -30,9 +28,6 @@
     <t>Рекомендации автору по устранению</t>
   </si>
   <si>
-    <t xml:space="preserve">ИТОГО ЗА СОДЕРЖАНИЕ: </t>
-  </si>
-  <si>
     <t>ОФОРМЛЕНИЕ</t>
   </si>
   <si>
@@ -54,9 +49,6 @@
     <t>НОМЕР ТЗ</t>
   </si>
   <si>
-    <t>Мнение о работе.</t>
-  </si>
-  <si>
     <t>Итого по работе</t>
   </si>
   <si>
@@ -120,18 +112,12 @@
     <t>ДОПОЛНИТЕЛЬНЫЕ КОММЕНТАРИИ</t>
   </si>
   <si>
-    <t>Соответствие объему по тз</t>
-  </si>
-  <si>
     <t>Нумерация страниц</t>
   </si>
   <si>
     <t>Признаки искусственного интеллекта</t>
   </si>
   <si>
-    <t>Соответствие методчике параметров страницы (поля)</t>
-  </si>
-  <si>
     <t>Межстрочный интервал</t>
   </si>
   <si>
@@ -150,16 +136,34 @@
     <t>Оформление таблиц и подписей к ним</t>
   </si>
   <si>
-    <t>Офомрление рисунков и подписей к ним</t>
-  </si>
-  <si>
-    <t>Офомрление приложений</t>
-  </si>
-  <si>
     <t>ИТОГО ЗА ОФОРМЛЕНИЕ</t>
   </si>
   <si>
     <t>Достаточность ссылок</t>
+  </si>
+  <si>
+    <t>Оформление приложений</t>
+  </si>
+  <si>
+    <t>Оформление рисунков и подписей к ним</t>
+  </si>
+  <si>
+    <t>Соответствие объему по ТЗ</t>
+  </si>
+  <si>
+    <t>Соответствие методичке параметров страницы (поля)</t>
+  </si>
+  <si>
+    <t>Мнение о работе</t>
+  </si>
+  <si>
+    <t>ИТОГО ЗА СОДЕРЖАНИЕ</t>
+  </si>
+  <si>
+    <t>Номера проверенных источников (на предмет их существования, соответствия содержания написанному в работе, работоспособности ссылок на интернет-ресурсы), не менее 20% от общего количества</t>
+  </si>
+  <si>
+    <t>Заключение по проверенным источникам</t>
   </si>
   <si>
     <t>Оформление оглавления</t>
@@ -168,8 +172,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,13 +204,6 @@
       <charset val="204"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -223,7 +220,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -248,8 +245,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -554,11 +557,157 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -581,9 +730,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -599,9 +745,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -614,10 +757,88 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -641,91 +862,49 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -751,9 +930,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -791,9 +970,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -828,7 +1007,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -863,7 +1042,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1036,59 +1215,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38.33203125" style="6" customWidth="1"/>
     <col min="2" max="2" width="55.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="44.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="44.44140625" style="1" customWidth="1"/>
     <col min="4" max="4" width="26.33203125" style="1" customWidth="1"/>
-    <col min="5" max="6" width="8.83203125" style="1"/>
-    <col min="7" max="7" width="42.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="54.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="35.1640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="38.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.83203125" style="1"/>
+    <col min="5" max="6" width="8.88671875" style="1"/>
+    <col min="7" max="7" width="42.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="54.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="35.109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="38.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:10" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
-      <c r="G1" s="39" t="s">
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="51"/>
+      <c r="G1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="26"/>
+    </row>
+    <row r="2" spans="1:10" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="29"/>
+      <c r="G2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="30"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+    </row>
+    <row r="3" spans="1:10" ht="32.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41"/>
-    </row>
-    <row r="2" spans="1:10" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="44"/>
-      <c r="G2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="47"/>
-    </row>
-    <row r="3" spans="1:10" ht="36" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="G3" s="5" t="s">
@@ -1098,338 +1279,363 @@
         <v>2</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="50"/>
-      <c r="G4" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="16"/>
-    </row>
-    <row r="5" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+    <row r="4" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A4" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="35"/>
+      <c r="G4" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="G5" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
     </row>
-    <row r="6" spans="1:10" ht="231" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
       <c r="G6" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
     </row>
-    <row r="7" spans="1:10" ht="97.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
+    <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
       <c r="G7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A8" s="51" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53"/>
+    <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="38"/>
       <c r="G8" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="1:10" ht="50.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+    <row r="9" spans="1:10" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
       <c r="G9" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
     </row>
-    <row r="10" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+    <row r="10" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
     </row>
-    <row r="11" spans="1:10" ht="150.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+    <row r="11" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
       <c r="G11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
     </row>
-    <row r="12" spans="1:10" ht="133.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+    <row r="12" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
       <c r="G12" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="178.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+    <row r="13" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
       <c r="G13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="G14" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-    </row>
-    <row r="15" spans="1:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="A15" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="31"/>
+    <row r="14" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="G14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A15" s="39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41"/>
       <c r="G15" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="11"/>
       <c r="G16" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="11"/>
       <c r="G17" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="1:10" ht="50.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
+    <row r="18" spans="1:10" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
       <c r="G18" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
     </row>
-    <row r="19" spans="1:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="13"/>
-      <c r="G19" s="54" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="56"/>
-    </row>
-    <row r="20" spans="1:10" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="13"/>
+    <row r="19" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="12"/>
+      <c r="G19" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="44"/>
+    </row>
+    <row r="20" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="12"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="20"/>
+      <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="29" t="s">
+    <row r="21" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A21" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="41"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="21"/>
+    </row>
+    <row r="22" spans="1:10" ht="46.35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="G22" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="21"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="21"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="G25" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="56"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="58"/>
+    </row>
+    <row r="26" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A26" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="31"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="36"/>
-    </row>
-    <row r="22" spans="1:10" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="G22" s="35" t="s">
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="41"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="62"/>
+    </row>
+    <row r="27" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="36"/>
-    </row>
-    <row r="23" spans="1:10" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-    </row>
-    <row r="24" spans="1:10" ht="132" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-    </row>
-    <row r="26" spans="1:10" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="31"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A27" s="32"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="34"/>
-    </row>
-    <row r="28" spans="1:10" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-    </row>
-    <row r="29" spans="1:10" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="22"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="24"/>
-    </row>
-    <row r="30" spans="1:10" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="24"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="54"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="62"/>
+    </row>
+    <row r="28" spans="1:10" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="48"/>
+      <c r="G28" s="65" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="66"/>
+      <c r="I28" s="63"/>
+      <c r="J28" s="64"/>
+    </row>
+    <row r="29" spans="1:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="46"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="48"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="22">
+    <mergeCell ref="G25:H27"/>
+    <mergeCell ref="I25:J27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="I22:J22"/>
@@ -1441,25 +1647,8 @@
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="G19:J19"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A27:D27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>